--- a/仕様/2Dアクション仕様.xlsx
+++ b/仕様/2Dアクション仕様.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="企画と仕様概略" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="195">
   <si>
     <r>
       <rPr>
@@ -1738,6 +1738,84 @@
   </si>
   <si>
     <t xml:space="preserve">攻撃ヒット</t>
+  </si>
+  <si>
+    <t xml:space="preserve">斬撃SE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">斬撃SE2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">斬撃SE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">被ダメージSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通常</t>
+  </si>
+  <si>
+    <t xml:space="preserve">殴打されたようなSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大ダメージ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">爆発音的なSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">移動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接地SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">足音SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ファンファーレ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">短時間のファンファーレSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">敵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボス戦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">激しめのBGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">打倒SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">連続爆発音</t>
+  </si>
+  <si>
+    <t xml:space="preserve">クリア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボス打倒後に流す短時間BGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その他</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タイトル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タイトル用、ちょっとファンタジックなもの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ゲームオーバー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">悲壮感あるBGM</t>
   </si>
   <si>
     <t xml:space="preserve">実習①の実装対応スケジュール</t>
@@ -2034,28 +2112,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2182,902 +2264,1062 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:F150"/>
+  <dimension ref="A2:F168"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.96"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+    <row r="7" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+    <row r="13" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+    <row r="15" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+    <row r="17" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
+    <row r="21" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="s">
+    <row r="26" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="1" t="s">
+    <row r="30" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0" t="s">
+    <row r="36" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="D37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E38" s="0" t="s">
+      <c r="E38" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D39" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E39" s="0" t="s">
+      <c r="D39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E40" s="0" t="s">
+      <c r="E40" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D43" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E43" s="0" t="s">
+      <c r="D43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="0" t="s">
+      <c r="C47" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D47" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E47" s="0" t="s">
+      <c r="D47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C48" s="0" t="s">
+    <row r="48" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C48" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D48" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" s="0" t="s">
+      <c r="D48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C49" s="0" t="s">
+      <c r="C49" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E49" s="0" t="s">
+      <c r="D49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D50" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E50" s="0" t="s">
+      <c r="D50" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C51" s="0" t="s">
+      <c r="C51" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D51" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E51" s="1" t="s">
+      <c r="D51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="0" t="s">
+      <c r="C55" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="D55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="0" t="s">
+      <c r="C56" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D56" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E56" s="0" t="s">
+      <c r="D56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C57" s="0" t="s">
+      <c r="C57" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E57" s="0" t="s">
+      <c r="D57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E58" s="0" t="s">
+      <c r="E58" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C59" s="0" t="s">
+      <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D59" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E59" s="0" t="s">
+      <c r="D59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="0" t="s">
+      <c r="C63" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D63" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E63" s="0" t="s">
+      <c r="D63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="0" t="s">
+      <c r="C64" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D64" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E64" s="0" t="s">
+      <c r="D64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E65" s="0" t="s">
+      <c r="E65" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E66" s="0" t="s">
+      <c r="E66" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C67" s="0" t="s">
+      <c r="C67" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D67" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E67" s="0" t="s">
+      <c r="D67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E68" s="0" t="s">
+      <c r="E68" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C69" s="0" t="s">
+      <c r="C69" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D69" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E69" s="0" t="s">
+      <c r="D69" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E70" s="0" t="s">
+      <c r="E70" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C71" s="0" t="s">
+      <c r="C71" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D71" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E71" s="0" t="s">
+      <c r="D71" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D72" s="0" t="s">
+      <c r="D72" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E72" s="0" t="s">
+      <c r="E72" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C73" s="0" t="s">
+    <row r="73" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C73" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D73" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E73" s="0" t="s">
+      <c r="D73" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C77" s="0" t="s">
+    <row r="77" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C77" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D77" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E77" s="0" t="s">
+      <c r="D77" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E78" s="0" t="s">
+    <row r="78" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E78" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E79" s="1" t="s">
+    <row r="79" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E79" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E80" s="0" t="s">
+      <c r="E80" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E81" s="0" t="s">
+      <c r="E81" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C82" s="0" t="s">
+    <row r="82" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C82" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D82" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E82" s="0" t="s">
+      <c r="D82" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="2" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E84" s="0" t="s">
+      <c r="E84" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E85" s="0" t="s">
+      <c r="E85" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="0" t="s">
+    <row r="88" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C88" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D88" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E88" s="0" t="s">
+      <c r="D88" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E89" s="0" t="s">
+      <c r="E89" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E90" s="0" t="s">
+      <c r="E90" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C91" s="0" t="s">
+      <c r="C91" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D91" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E91" s="0" t="s">
+      <c r="D91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E92" s="0" t="s">
+      <c r="E92" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="3" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C96" s="0" t="s">
+      <c r="C96" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D96" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E96" s="0" t="s">
+      <c r="D96" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="97" s="3" customFormat="true" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="0"/>
-      <c r="C97" s="0"/>
-      <c r="D97" s="0"/>
-      <c r="E97" s="1" t="s">
+    <row r="97" s="4" customFormat="true" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F97" s="0"/>
-    </row>
-    <row r="98" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="0"/>
-      <c r="E98" s="0" t="s">
+      <c r="F97" s="1"/>
+    </row>
+    <row r="98" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="1"/>
+      <c r="E98" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F98" s="0"/>
+      <c r="F98" s="1"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="0" t="s">
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C100" s="0" t="s">
+      <c r="C100" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D100" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E100" s="1" t="s">
+      <c r="D100" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C101" s="0" t="s">
+      <c r="C101" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D101" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E101" s="1" t="s">
+      <c r="D101" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E102" s="0" t="s">
+      <c r="E102" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C103" s="0" t="s">
+      <c r="C103" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D103" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E103" s="0" t="s">
+      <c r="D103" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E104" s="0" t="s">
+      <c r="E104" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C105" s="0" t="s">
+      <c r="C105" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D105" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E105" s="0" t="s">
+      <c r="D105" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E106" s="0" t="s">
+      <c r="E106" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C108" s="0" t="s">
+      <c r="C108" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D108" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E108" s="4" t="s">
+      <c r="D108" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E108" s="5" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C109" s="0" t="s">
+      <c r="C109" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D109" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E109" s="0" t="s">
+      <c r="D109" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E110" s="0" t="s">
+      <c r="E110" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E111" s="0" t="s">
+      <c r="E111" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E112" s="0" t="s">
+      <c r="E112" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
+      <c r="A116" s="1" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="0" t="s">
+      <c r="B117" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D119" s="0" t="s">
+      <c r="D119" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E119" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F119" s="0" t="s">
+      <c r="E119" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D120" s="0" t="s">
+      <c r="D120" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E120" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F120" s="0" t="s">
+      <c r="E120" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F121" s="0" t="s">
+      <c r="F121" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D123" s="0" t="s">
+      <c r="D123" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E123" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F123" s="0" t="s">
+      <c r="E123" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D125" s="2" t="s">
+      <c r="D125" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D126" s="0" t="s">
+      <c r="D126" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E126" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F126" s="1" t="s">
+      <c r="E126" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F126" s="2" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D127" s="0" t="s">
+      <c r="D127" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E127" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F127" s="1" t="s">
+      <c r="E127" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F127" s="2" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D128" s="0" t="s">
+      <c r="D128" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E128" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F128" s="1" t="s">
+      <c r="E128" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C130" s="0" t="s">
+      <c r="C130" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D131" s="0" t="s">
+      <c r="D131" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E131" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F131" s="0" t="s">
+      <c r="E131" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D132" s="0" t="s">
+      <c r="D132" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E132" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F132" s="0" t="s">
+      <c r="E132" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C133" s="0" t="s">
+      <c r="C133" s="1" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D134" s="0" t="s">
+      <c r="D134" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E134" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F134" s="0" t="s">
+      <c r="E134" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D135" s="0" t="s">
+      <c r="D135" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E135" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F135" s="0" t="s">
+      <c r="E135" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D139" s="0" t="s">
+      <c r="D139" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E139" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F139" s="0" t="s">
+      <c r="E139" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F140" s="0" t="s">
+      <c r="F140" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C142" s="0" t="s">
+      <c r="C142" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D143" s="0" t="s">
+      <c r="D143" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E143" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F143" s="0" t="s">
+      <c r="E143" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D144" s="0" t="s">
+      <c r="D144" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E144" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F144" s="0" t="s">
+      <c r="E144" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F144" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="0" t="s">
+      <c r="A146" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="1" t="s">
+      <c r="B147" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C148" s="0" t="s">
+    <row r="148" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C148" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D148" s="0" t="s">
+      <c r="D148" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D149" s="0" t="s">
+      <c r="E148" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F148" s="0" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D149" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D150" s="0" t="s">
+      <c r="E149" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F149" s="0" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D150" s="1" t="s">
         <v>125</v>
+      </c>
+      <c r="E150" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F150" s="0" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C152" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D152" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E152" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F152" s="0" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D153" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="E153" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F153" s="0" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C155" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D155" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F155" s="0" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D156" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F156" s="0" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C158" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D158" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="E158" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F158" s="0" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B160" s="0" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C161" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D161" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="E161" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F161" s="0" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D162" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="E162" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F162" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C164" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D164" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="E164" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F164" s="0" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B166" s="0" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C167" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D167" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="E167" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F167" s="0" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C168" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D168" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="E168" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F168" s="0" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -3099,188 +3341,188 @@
   <dimension ref="B2:D20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36.54"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
-        <v>149</v>
+      <c r="B2" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>151</v>
+      <c r="C3" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>46160</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>152</v>
+      <c r="C4" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>46161</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>153</v>
+      <c r="C5" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>46162</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>154</v>
+      <c r="C6" s="1" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>46163</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>156</v>
+      <c r="C7" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>46164</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>156</v>
+      <c r="C8" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>46165</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>158</v>
+      <c r="C9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>46166</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>158</v>
+      <c r="C10" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>46167</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>159</v>
+      <c r="C11" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>46168</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>160</v>
+      <c r="C12" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>46169</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>162</v>
+      <c r="C13" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>46170</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>164</v>
+      <c r="C14" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>46171</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>166</v>
+      <c r="C15" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>46172</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>166</v>
+      <c r="C16" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>46173</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>166</v>
+      <c r="C17" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>46174</v>
       </c>
-      <c r="C18" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>166</v>
+      <c r="C18" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>46175</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>167</v>
+      <c r="C19" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>46176</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>168</v>
+      <c r="C20" s="1" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/仕様/2Dアクション仕様.xlsx
+++ b/仕様/2Dアクション仕様.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="242">
   <si>
     <r>
       <rPr>
@@ -477,7 +477,43 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">、攻撃力、防御力</t>
+      <t xml:space="preserve">、攻撃力、防御力　※実装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">では</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">HP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">と攻撃力以外の使い道は特にない</t>
     </r>
   </si>
   <si>
@@ -490,51 +526,7 @@
     <t xml:space="preserve">敵を倒すと経験値が入手、一定値溜まるとレベルアップ</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">最大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">50Lv</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">Lv</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">が上がると与ダメージが上がり被ダメージが下がる</t>
-    </r>
+    <t xml:space="preserve">最大50Lv、Lvが上がると与ダメージが上がり被ダメージが下がる　※実装1では最大Lv2まで</t>
   </si>
   <si>
     <t xml:space="preserve">アイテム</t>
@@ -1445,6 +1437,111 @@
   </si>
   <si>
     <t xml:space="preserve">ChatGptによる、ゲーム画面のイメージ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デバッグUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">攻撃範囲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ひとまずはScene側だけでも表示させる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCのパラメータ表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数値だけ画面どこかにテキスト表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">敵のパラメータ表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">敵オブジェクトの頭上にHP数値表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メニュー画面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メニュー仕様</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所持アイテムと装備品の表示、画面裏のゲームは停止</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メニュー画面構成仕様</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面左部にメニュー項目が並び、中央から右は項目に即した内容の表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アイテム画面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メニューTOPを兼用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道中拾ったり買ったアイテムを一覧で表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4＊3行の12種表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1種最大9個まで所持可能</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アイテムアイコンの下にアイテム名と個数表記</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCパラメータ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC名、最大HP、最大MP、攻撃力、防御力を表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マップ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">優先度最低</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ステージのマップを確認できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全オープン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ショップ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ショップ仕様</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ステージにある扉から入る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メニューのアイテム画面の流用（背景違いとか)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">回復アイテムやスペシャルアイテムが並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アイテムアイコンの下に、アイテム名と値段表記</t>
+  </si>
+  <si>
+    <t xml:space="preserve">購入フロー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アイテムをカーソル移動させて選択</t>
+  </si>
+  <si>
+    <t xml:space="preserve">選択しているときに攻撃ボタン（決定ボタン）を押すと</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何個買うか確認の流れ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">個数選択のウィンドウが出て、数値を選択して決定すると最終確認。決定するとアイテム入手＋所持金減額。</t>
   </si>
   <si>
     <t xml:space="preserve">◆エフェクト</t>
@@ -2200,9 +2297,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>41400</xdr:colOff>
+      <xdr:colOff>41040</xdr:colOff>
       <xdr:row>137</xdr:row>
-      <xdr:rowOff>108360</xdr:rowOff>
+      <xdr:rowOff>108000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2216,7 +2313,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="781920" y="20400120"/>
-          <a:ext cx="3979440" cy="2539080"/>
+          <a:ext cx="3979080" cy="2538720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2343,7 +2440,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:F193"/>
+  <dimension ref="A2:F220"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.94"/>
@@ -3080,388 +3177,582 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="0" t="s">
+      <c r="B122" s="1" t="s">
         <v>128</v>
       </c>
     </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="0" t="s">
+        <v>129</v>
+      </c>
+    </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="1" t="s">
-        <v>129</v>
+      <c r="C141" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E141" s="0" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C143" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D144" s="1" t="s">
+      <c r="C142" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E144" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F144" s="1" t="s">
+      <c r="D142" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E142" s="0" t="s">
         <v>133</v>
       </c>
     </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C143" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E143" s="0" t="s">
+        <v>135</v>
+      </c>
+    </row>
     <row r="145" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D145" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F146" s="1" t="s">
+      <c r="B145" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="0" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C147" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C148" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="D148" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D150" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D151" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F151" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E148" s="0" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D152" s="1" t="s">
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C149" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E152" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F152" s="2" t="s">
+      <c r="D149" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E149" s="0" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D153" s="1" t="s">
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E150" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="E153" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F153" s="2" t="s">
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E151" s="0" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C152" s="0"/>
+      <c r="D152" s="0"/>
+      <c r="E152" s="0" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C153" s="0"/>
+      <c r="D153" s="0"/>
+      <c r="E153" s="0" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C154" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E154" s="0" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C155" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D156" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>147</v>
+      <c r="E156" s="0" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D157" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>149</v>
+      <c r="E157" s="0" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C158" s="1" t="s">
-        <v>150</v>
+      <c r="B158" s="0" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C159" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="D159" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>151</v>
+        <v>22</v>
+      </c>
+      <c r="E159" s="0" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D160" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C163" s="3" t="s">
-        <v>53</v>
+      <c r="E160" s="0" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E161" s="0" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E162" s="0" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C163" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E163" s="0" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D164" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>154</v>
+      <c r="E164" s="0" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F165" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C167" s="1" t="s">
-        <v>155</v>
+      <c r="E165" s="0" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E166" s="0" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D168" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>154</v>
+      <c r="A168" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D169" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B172" s="2" t="s">
-        <v>159</v>
+      <c r="B169" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C170" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D171" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D172" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C173" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F173" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="174" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D174" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D175" s="1" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C177" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D177" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D178" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F178" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C180" s="1" t="s">
-        <v>169</v>
-      </c>
+      <c r="F178" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D179" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D180" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F180" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D181" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>171</v>
+      <c r="F180" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C182" s="1" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C183" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D183" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D184" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B185" s="1" t="s">
-        <v>174</v>
+      <c r="C185" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C186" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="D186" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D187" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C189" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C190" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B191" s="1" t="s">
-        <v>182</v>
+      <c r="D191" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C192" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F192" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C193" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C194" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D195" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D196" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B199" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C200" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D201" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D202" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C204" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D205" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C207" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D208" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C210" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B212" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C213" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D214" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C216" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B218" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C219" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C220" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3491,15 +3782,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="1" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>189</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3507,7 +3798,7 @@
         <v>46160</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3515,7 +3806,7 @@
         <v>46161</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3523,7 +3814,7 @@
         <v>46162</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3531,10 +3822,10 @@
         <v>46163</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3542,10 +3833,10 @@
         <v>46164</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3553,10 +3844,10 @@
         <v>46165</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3564,10 +3855,10 @@
         <v>46166</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3575,7 +3866,7 @@
         <v>46167</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3583,7 +3874,7 @@
         <v>46168</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3591,10 +3882,10 @@
         <v>46169</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3602,10 +3893,10 @@
         <v>46170</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3613,10 +3904,10 @@
         <v>46171</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3624,10 +3915,10 @@
         <v>46172</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3635,10 +3926,10 @@
         <v>46173</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3646,10 +3937,10 @@
         <v>46174</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3657,7 +3948,7 @@
         <v>46175</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3665,7 +3956,7 @@
         <v>46176</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
